--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_930_Costa_Rica_Pacific.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_930_Costa_Rica_Pacific.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4bbe6ff8cc7b45bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rdd7bf450773242c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R17d821a58254457c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R685be7ab6f904645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R519b0f45da3c45d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Race1f3b17d8b4e83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb9364feafeed4411"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8f95156837c04f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rebd6eb77389e4279"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R88fc87bda5444eb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1c4200b8453243cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf9867789abb043aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ930CommercialTable" displayName="EEZ930CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ930CommercialTable" displayName="EEZ930CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ930FunctionalTable" displayName="EEZ930FunctionalTable" ref="A1:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O16"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ930FunctionalTable" displayName="EEZ930FunctionalTable" ref="A1:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E16"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ930ValidationTable" displayName="EEZ930ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ930ValidationTable" displayName="EEZ930ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4915,7 +4869,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce9242e9577e4baf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3cf4107d1362427e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4925,20 +4879,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4946,444 +4890,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4716.2667498030005</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.573934987353051</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>37.491687405629484</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4716.2667498030005</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>39.155861680337644</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$64,A2,'Species'!$U$2:$U$64))</x:f>
-        <x:v>184669.48850286187</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.573934987353051</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>37.491687405629484</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>176820.79870517825</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>7848.689797683619</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.044387820070704</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.04438782007070398</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>847.4675376890001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.9602061855684005</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>912.4439282528331</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>847.4675376890001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>948.3963811138564</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$64,A3,'Species'!$U$2:$U$64))</x:f>
-        <x:v>803735.1458557184</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.9602061855684005</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>912.4439282528331</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>773266.6091557071</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>30468.536700011347</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.039402369556961</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.039402369556961074</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>6499.4741898551</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.397204696906725</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>249.57707865150735</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>6499.4741898551</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>414.99952774711727</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$64,A4,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2697278.719394444</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.397204696906725</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>249.57707865150735</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1622119.7810749083</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1075158.9383195357</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.6628110641786729</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.6628110641786727</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2831.1963345280997</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.972253409715255</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>938.1092315865465</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2831.1963345280997</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1105.0365398055937</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$64,A5,'Species'!$U$2:$U$64))</x:f>
-        <x:v>3128575.4010172114</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.972253409715255</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>938.1092315865465</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2655971.4178548027</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>472603.9831624087</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1779401615489242</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.17794016154892414</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>329.0853325</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.4999999999999996</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>316.2277660168376</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>329.0853325</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$64,A6,'Species'!$U$2:$U$64))</x:f>
-        <x:v>104065.91952538332</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.4999999999999996</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>316.2277660168376</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>104065.9195253832</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1.1641532182693481e-10</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>1.1186690355293447e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>24661.8517126458</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.113208439401327</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1297.8020008998565</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>24661.8517126458</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1431.408356565885</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$64,A7,'Species'!$U$2:$U$64))</x:f>
-        <x:v>35301180.62986988</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.113208439401327</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1297.8020008998565</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>32006200.498567272</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3294980.1313026063</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1029481812891255</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.10294818128912563</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>13831.651338880498</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.431779595492117</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2702.5864530279428</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>13831.651338880498</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2751.6643539001648</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$64,A8,'Species'!$U$2:$U$64))</x:f>
-        <x:v>38060061.94477295</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.431779595492117</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2702.5864530279428</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>37381233.53146424</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>678828.4133087099</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0181596044105214</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.018159604410521436</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99e36cf8ac3b4069"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e2a8883a3d64005"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5393,20 +5048,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5414,876 +5059,307 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>8.585643993</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.815521551766955</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>653.9153796046813</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>8.585643993</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>789.9379926824004</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$64,A2,'Species'!$U$2:$U$64))</x:f>
-        <x:v>6782.126381716128</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.815521551766955</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>653.9153796046813</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>5614.284650833247</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1167.8417308828812</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.2080125614417423</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.20801256144174224</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1143.0899834400002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.0091717490660264</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>102.13433112632241</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1143.0899834400002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>102.68224679584021</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$64,A3,'Species'!$U$2:$U$64))</x:f>
-        <x:v>117375.047789439</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.0091717490660264</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>102.13433112632241</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>116748.73087584338</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>626.3169135956268</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.005364657147851</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.005364657147851008</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>107.3493416</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.07</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1174.8975549395302</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>107.3493416</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1174.8975549395302</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$64,A4,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>126124.4789702084</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.07</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1174.8975549395302</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>126124.4789702084</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>14157.5513880133</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.430626279000435</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2695.4189603862255</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>14157.5513880133</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2744.069264191652</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$64,A5,'Species'!$U$2:$U$64))</x:f>
-        <x:v>38849301.62006116</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.430626279000435</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2695.4189603862255</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>38160532.44389337</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>688769.1761677861</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0180492548729625</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0180492548729625</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>24661.8517126458</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.113208439401327</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1297.8020008998565</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>24661.8517126458</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1431.408356565885</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$64,A6,'Species'!$U$2:$U$64))</x:f>
-        <x:v>35301180.62986988</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.113208439401327</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1297.8020008998565</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>32006200.498567272</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3294980.1313026063</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1029481812891255</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.10294818128912563</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.059394103</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>39.810717055349734</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.059394103</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$64,A7,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2.364521829289299</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>2.364521829289299</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>322.94101334000004</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.010529896995212</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1024.5423077599685</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>322.94101334000004</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1189.2864140963356</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$64,A8,'Species'!$U$2:$U$64))</x:f>
-        <x:v>384069.35971976555</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.010529896995212</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1024.5423077599685</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>330866.7310777064</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>53202.628642059164</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1607977582658928</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.1607977582658927</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>5827.183831376399</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4926090943815935</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>310.8916761742366</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>5827.183831376399</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>480.22147195155446</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$64,A9,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2798338.7968358733</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4926090943815935</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>310.8916761742366</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1811622.9487120188</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>986715.8481238545</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5446585056925695</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5446585056925695</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>3.8762397520000005</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4067462938899755</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>255.12105013422874</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>3.8762397520000005</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>298.7139236573791</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$64,A10,'Species'!$U$2:$U$64))</x:f>
-        <x:v>1157.8867853566262</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4067462938899755</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>255.12105013422874</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>988.9103561022825</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>168.97642925434366</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1708713314727048</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.1708713314727048</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1153.39051685</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.019839006201553</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1046.7404474265327</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1153.39051685</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1047.5629301688866</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$64,A11,'Species'!$U$2:$U$64))</x:f>
-        <x:v>1208249.1494603925</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.019839006201553</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1046.7404474265327</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1207300.5056650888</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>948.6437953037675</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.000785756148409</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0007857561484091071</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4716.2073557</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.5739346591002983</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>37.49165906830205</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4716.2073557</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>39.15585343334071</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$64,A12,'Species'!$U$2:$U$64))</x:f>
-        <x:v>184667.12398103258</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.5739346591002983</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>37.49165906830205</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>176818.43827532275</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>7848.685705709824</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0443883894816937</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.04438838948169359</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>8.736778739</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>8.736778739</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$64,A13,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>2762.8120228173766</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>2762.8120228173766</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>709.99744926</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.743033478002272</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>553.3927663781337</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>709.99744926</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>678.0549077466495</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$64,A14,'Species'!$U$2:$U$64))</x:f>
-        <x:v>481417.2549583458</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.743033478002272</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>553.3927663781337</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>392907.4525674101</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>88509.80239093571</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2252688306433952</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.22526883064339515</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>48.705009399999994</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.1956918618067247</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>156.92490044695455</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>48.705009399999994</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>295.7283429846324</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$64,A15,'Species'!$U$2:$U$64))</x:f>
-        <x:v>14403.451724912942</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.1956918618067247</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>156.92490044695455</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>7643.028751362985</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>6760.4229735499575</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.8845214630841691</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.8845214630841691</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>847.4675376890001</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.9602061855684005</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>912.4439282528331</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>847.4675376890001</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>948.3963811138564</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$64,A16,'Species'!$U$2:$U$64))</x:f>
-        <x:v>803735.1458557184</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.9602061855684005</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>912.4439282528331</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>773266.6091557071</x:v>
       </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>30468.536700011347</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.039402369556961</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.039402369556961074</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G16">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O16">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a29acf2224c4333"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b62634f9b8e4fe2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6458,7 +5534,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6557,7 +5633,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>80279567.24893844</x:v>
+        <x:v>74719678.55634749</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6571,7 +5647,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>80279567.24893846</x:v>
+        <x:v>75119400.23806289</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6585,7 +5661,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.4901161193847656e-8</x:v>
+        <x:v>-5559888.692590967</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6599,7 +5675,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-5160167.010875568</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6610,9 +5686,9 @@
         <x:v>EEZ_930</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6624,47 +5700,19 @@
         <x:v>EEZ_930</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_930</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_930</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99defdb8b34d47ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b0bc2da463c4fbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6711,7 +5759,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
